--- a/diseases/d120/2010-2014.xlsx
+++ b/diseases/d120/2010-2014.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2191,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2780,6 @@
       <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.0082018756356774</v>
       </c>
@@ -3381,9 +3369,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3958,6 @@
       <c r="O23" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -4565,9 +4547,6 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -5157,9 +5136,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5749,9 +5725,6 @@
       <c r="O35" t="n">
         <v>3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -6341,9 +6314,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6933,9 +6903,6 @@
       <c r="O43" t="n">
         <v>2</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -7525,9 +7492,6 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -8117,9 +8081,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -8709,9 +8670,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9105,9 +9063,6 @@
       <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -9697,9 +9652,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10289,9 +10241,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -10881,9 +10830,6 @@
       <c r="O69" t="n">
         <v>1</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -11473,9 +11419,6 @@
       <c r="O73" t="n">
         <v>3</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.006106541625592117</v>
       </c>
@@ -12065,9 +12008,6 @@
       <c r="O77" t="n">
         <v>2</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -12657,9 +12597,6 @@
       <c r="O81" t="n">
         <v>2</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -13249,9 +13186,6 @@
       <c r="O85" t="n">
         <v>3</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.006106541625592117</v>
       </c>
@@ -13841,9 +13775,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14433,9 +14364,6 @@
       <c r="O93" t="n">
         <v>3</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.006106541625592117</v>
       </c>
@@ -15025,9 +14953,6 @@
       <c r="O97" t="n">
         <v>2</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -15617,9 +15542,6 @@
       <c r="O101" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -16209,9 +16131,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16605,9 +16524,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -16753,9 +16669,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -17593,9 +17506,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17741,9 +17651,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -18581,9 +18488,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -18729,9 +18633,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -19569,9 +19470,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -19717,9 +19615,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -20557,9 +20452,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20705,9 +20597,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -21545,9 +21434,6 @@
       <c r="O137" t="n">
         <v>4</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.008064584499148828</v>
       </c>
@@ -21693,9 +21579,6 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -22533,9 +22416,6 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -22681,9 +22561,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -23521,9 +23398,6 @@
       <c r="O149" t="n">
         <v>2</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -23669,9 +23543,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -24509,9 +24380,6 @@
       <c r="O155" t="n">
         <v>2</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -24657,9 +24525,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -25941,9 +25806,6 @@
       <c r="O164" t="n">
         <v>3</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.00604843837436162</v>
       </c>
@@ -26089,9 +25951,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -27521,9 +27380,6 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -27669,9 +27525,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -29249,9 +29102,6 @@
       <c r="O185" t="n">
         <v>3</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.00604843837436162</v>
       </c>
@@ -29397,9 +29247,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -30977,9 +30824,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -31373,9 +31217,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -32705,9 +32546,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -33889,9 +33727,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -35073,9 +34908,6 @@
       <c r="O223" t="n">
         <v>3</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -36257,9 +36089,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -37589,9 +37418,6 @@
       <c r="O240" t="n">
         <v>2</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -38773,9 +38599,6 @@
       <c r="O248" t="n">
         <v>7</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.013980102260254</v>
       </c>
@@ -39957,9 +39780,6 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -41289,9 +41109,6 @@
       <c r="O265" t="n">
         <v>1</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -42473,9 +42290,6 @@
       <c r="O273" t="n">
         <v>3</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -43805,9 +43619,6 @@
       <c r="O282" t="n">
         <v>3</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -44989,9 +44800,6 @@
       <c r="O290" t="n">
         <v>2</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -46321,9 +46129,6 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
@@ -46717,9 +46522,6 @@
       <c r="O301" t="n">
         <v>2</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -46865,9 +46667,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -48445,9 +48244,6 @@
       <c r="O312" t="n">
         <v>3</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.005936003295510736</v>
       </c>
@@ -48593,9 +48389,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -50025,9 +49818,6 @@
       <c r="O322" t="n">
         <v>2</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -50173,9 +49963,6 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -51605,9 +51392,6 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
@@ -51753,9 +51537,6 @@
       <c r="O333" t="n">
         <v>0</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0</v>
       </c>
@@ -53185,9 +52966,6 @@
       <c r="O342" t="n">
         <v>3</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0.005936003295510736</v>
       </c>
@@ -53333,9 +53111,6 @@
       <c r="O343" t="n">
         <v>0</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0</v>
       </c>
@@ -54913,9 +54688,6 @@
       <c r="O353" t="n">
         <v>5</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.009893338825851227</v>
       </c>
@@ -55061,9 +54833,6 @@
       <c r="O354" t="n">
         <v>1</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -56493,9 +56262,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -56641,9 +56407,6 @@
       <c r="O364" t="n">
         <v>0</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0</v>
       </c>
@@ -58221,9 +57984,6 @@
       <c r="O374" t="n">
         <v>3</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.005936003295510736</v>
       </c>
@@ -58369,9 +58129,6 @@
       <c r="O375" t="n">
         <v>0</v>
       </c>
-      <c r="Q375" t="n">
-        <v>0</v>
-      </c>
       <c r="R375" t="n">
         <v>0</v>
       </c>
@@ -59801,9 +59558,6 @@
       <c r="O384" t="n">
         <v>2</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -59949,9 +59703,6 @@
       <c r="O385" t="n">
         <v>0</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>0</v>
       </c>
@@ -61381,9 +61132,6 @@
       <c r="O394" t="n">
         <v>2</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -61529,9 +61277,6 @@
       <c r="O395" t="n">
         <v>0</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0</v>
       </c>
@@ -63109,9 +62854,6 @@
       <c r="O405" t="n">
         <v>1</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -63257,9 +62999,6 @@
       <c r="O406" t="n">
         <v>0</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0</v>
       </c>
@@ -64689,9 +64428,6 @@
       <c r="O415" t="n">
         <v>0</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0</v>
       </c>
@@ -64835,9 +64571,6 @@
         <v>0</v>
       </c>
       <c r="O416" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q416" t="n">
         <v>0</v>
       </c>
       <c r="R416" t="n">
